--- a/PhIPSeq_Control_Template_v1.xlsx
+++ b/PhIPSeq_Control_Template_v1.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D35"/>
+  <dimension ref="B2:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -585,53 +585,43 @@
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>Column names are read by meaning, so this run’s file can say replicates, n_wells or wells/plate instead of wells_per_plate, and priority or seq instead of order. Nothing here is fixed for every run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>Set wells_per_plate to 0 to import a control without putting it in the layout — useful for one you keep on hand but are not running this time.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Required?</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>sample_id</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Your name for the control. Appears in the Lab Plate Maps. Must be unique in this file.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Required</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>sample_type</t>
+          <t>sample_id</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>mAb, control, or assay control. Anything else is refused: a patient sample in a control file is the wrong file.</t>
+          <t>Your name for the control. Appears in the Lab Plate Maps. Must be unique in this file.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -643,46 +633,46 @@
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>sample_type</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Any control type, including one of your own. Recognised specimen types (serum, plasma, whole blood, CSF) are refused — a patient sample in a control file is the wrong file.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>wells_per_plate</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>How many wells this control takes on EVERY plate, 0-4.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>How many wells this control takes on EVERY plate. Any count the control area can hold.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Order within the control area, lowest first. Blank falls back to row order.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>cohort</t>
+          <t>order</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Grouping and colour, e.g. "Lab controls". Controls are never auto-filled, so this only affects how they read.</t>
+          <t>Order within the control area, lowest first. Blank falls back to row order. Also read from priority, sort_order, seq.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -694,12 +684,12 @@
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>volume_mL</t>
+          <t>cohort</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Volume on hand, for the volume pre-flight check.</t>
+          <t>Grouping and colour, e.g. "Lab controls". Controls are never auto-filled, so this only affects how they read.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -711,29 +701,29 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>min_volume_required_mL</t>
+          <t>volume_mL</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Per-control override of the volume floor.</t>
+          <t>Volume on hand, for the volume pre-flight check.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>repeat_across_plates</t>
+          <t>min_volume_required_mL</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>"all"/"yes", or a plate list such as 1,3,5. Marks a bridging control.</t>
+          <t>Per-control override of the volume floor.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -745,12 +735,12 @@
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>source_rack / source_position</t>
+          <t>repeat_across_plates</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Where the tube sits, for the worklist and Tecan exports.</t>
+          <t>"all"/"yes", or a plate list such as 1,3,5. Marks a bridging control.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -762,12 +752,12 @@
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>subject_id</t>
+          <t>source_rack / source_position</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Usually blank for a control. If given, tiu_id becomes sample_id_subject_id.</t>
+          <t>Where the tube sits, for the worklist and Tecan exports.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -779,32 +769,41 @@
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>subject_id</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Usually blank for a control. If given, tiu_id becomes sample_id_subject_id.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Anything else — lot number, catalogue number, supplier. Carried into the export.</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>What the designer does with it</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Rows are merged into the sample pool as controls, so the control template can place them.</t>
         </is>
       </c>
     </row>
@@ -812,7 +811,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>A row that is not a control type is refused and named, rather than quietly added.</t>
+          <t>Rows are merged into the sample pool as controls, so the control template can place them.</t>
         </is>
       </c>
     </row>
@@ -820,7 +819,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Re-importing the same file does not duplicate: rows already present are left alone.</t>
+          <t>A control type this tool has never heard of is accepted and reported. A patient specimen type is refused and named.</t>
         </is>
       </c>
     </row>
@@ -828,7 +827,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Imported controls are written into the exported Input Samples sheet with a note naming this file, so the exported manifest still re-opens on its own.</t>
+          <t>Re-importing the same file does not duplicate: rows already present are left alone.</t>
         </is>
       </c>
     </row>
@@ -836,36 +835,44 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>Imported controls are written into the exported Input Samples sheet with a note naming this file, so the exported manifest still re-opens on its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>Controls are never auto-filled. They are stamped into the reserved control area.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Colour Legend</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr"/>
-      <c r="C33" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Yellow = you fill this in</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="7" t="inlineStr"/>
-      <c r="C34" s="6" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr"/>
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Blue italic row 2 = example, delete before uploading</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="8" t="inlineStr"/>
-      <c r="C35" s="6" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="8" t="inlineStr"/>
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Red = a required value is missing on a row that has other data</t>
         </is>
@@ -1588,12 +1595,12 @@
     <dataValidation sqref="A3:A41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="sample_id" error="sample_id is required and must be unique within this file. It is how the control is named on the Lab Plate Maps." type="custom">
       <formula1>=AND(LEN(TRIM($A3))&gt;0,COUNTIF($A$3:$A$41,$A3)&lt;=1)</formula1>
     </dataValidation>
-    <dataValidation sqref="B3:B41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="sample_type" error="A control file holds control types only: mAb, control or assay control. Anything else is refused on import." type="list">
+    <dataValidation sqref="B3:B41" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="sample_type" prompt="Pick one, or type your own — a pooled reference, an IVIG standard, a titration ladder. Any type the designer does not recognise is taken as a control. Do not put a specimen type here (serum, plasma, whole blood, CSF): those are refused, because that is how a sample manifest gets loaded as a control file by mistake." type="list">
       <formula1>"mAb,control,assay control"</formula1>
     </dataValidation>
-    <dataValidation sqref="C3:C41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="wells_per_plate" error="How many wells this control takes on EVERY plate, 0 to 4. 0 imports the control but leaves it out of the layout." type="whole" operator="between">
+    <dataValidation sqref="C3:C41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="wells_per_plate" error="How many wells this control takes on EVERY plate. A plate holds 96, and the control area has to be big enough — the designer checks the fit and can size the area to this file. 0 imports the control but leaves it out of the layout." type="whole" operator="between">
       <formula1>0</formula1>
-      <formula2>4</formula2>
+      <formula2>96</formula2>
     </dataValidation>
     <dataValidation sqref="D3:D41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="order" error="The order controls are laid into the control area, lowest first. Leave blank to use the row order." type="whole" operator="between">
       <formula1>1</formula1>
